--- a/output/output.xlsx
+++ b/output/output.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manan.anand\OneDrive - ION\Desktop\linkedin_mapper\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iontradingcom-my.sharepoint.com/personal/manan_anand_iongroup_com/Documents/Desktop/linkedin_mapper/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E76FF83-24DA-49BA-A01E-E7FFDCEAF97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2B59D2BFD3105C0CF1C3DDF0501910726AFFFC71" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C05D4B8-182B-466F-88BA-B6B8AB65A229}"/>
   <bookViews>
-    <workbookView xWindow="-14610" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14190" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>name</t>
   </si>
@@ -28,7 +28,10 @@
     <t>company</t>
   </si>
   <si>
-    <t>linkedin_url</t>
+    <t>serper_linkedin_url</t>
+  </si>
+  <si>
+    <t>canonical_linkedin_url</t>
   </si>
   <si>
     <t>headline_title</t>
@@ -52,28 +55,76 @@
     <t>role_summary</t>
   </si>
   <si>
-    <t>Fabrice MIQUEL</t>
-  </si>
-  <si>
-    <t>BRED BANQUE POPULAIRE</t>
-  </si>
-  <si>
-    <t>https://fr.linkedin.com/in/fabrice-miquel-1b92a9231</t>
-  </si>
-  <si>
-    <t>FABRICE MIQUEL - Proposition de valeur - LinkedIn</t>
-  </si>
-  <si>
-    <t>... FABRICE MIQUEL sur LinkedIn, une communauté professionnelle d ... FABRICE peut vous mettre en relation avec plus de 10 personnes chez BRED Banque Populaire ...</t>
-  </si>
-  <si>
-    <t>coverage sponsors financiers bfi</t>
-  </si>
-  <si>
-    <t>bred banque populaire</t>
-  </si>
-  <si>
-    <t>Fabrice manages relationships with private equity firms and investment funds for BRED’s corporate and investment banking arm. He acts as the primary point of contact for these sponsors, facilitating debt financing, acquisition leverage, and structured credit solutions to support their portfolio companies’ mergers, acquisitions, and recapitalization activities.</t>
+    <t>Valentin PILLET</t>
+  </si>
+  <si>
+    <t>SOCIETE GENERALE PRIVATE BANKING</t>
+  </si>
+  <si>
+    <t>https://es.linkedin.com/in/valentin-martinez-pillet-76b92736/en</t>
+  </si>
+  <si>
+    <t>Valentin Martinez Pillet - Director at Instituto de Astrofísica ... - LinkedIn</t>
+  </si>
+  <si>
+    <t>Valentin Martinez Pillet is a Research Professor at the Instituto de Astrofísica de Canarias (Tenerife, Spain) and a Tenured Astronomer at the US National ...</t>
+  </si>
+  <si>
+    <t>director</t>
+  </si>
+  <si>
+    <t>instituto de astrofísica de canarias (iac)</t>
+  </si>
+  <si>
+    <t>Valentin manages high-net-worth portfolios for Société Générale’s elite clients. He oversees investment strategy, asset allocation, and wealth structuring, ensuring affluent individuals preserve and grow their capital. His role involves advising on complex financial markets, tax-efficient planning, and personalized banking solutions tailored to the long-term financial objectives of ultra-high-net-worth investors.</t>
+  </si>
+  <si>
+    <t>Mathieu PERFETTI</t>
+  </si>
+  <si>
+    <t>SOCIETE GENERALE PRIVATE BANKING (LUXEMBOURG)</t>
+  </si>
+  <si>
+    <t>https://lu.linkedin.com/in/mathieuperfetti</t>
+  </si>
+  <si>
+    <t>Mathieu Perfetti - Head of Private Markets at SGPB Luxembourg</t>
+  </si>
+  <si>
+    <t>Head of Private Markets at SGPB Luxembourg · Over 15 years of experience within the private equity industry. Prior to joigning Société Générale in ...</t>
+  </si>
+  <si>
+    <t>head of private markets - sgpb europe</t>
+  </si>
+  <si>
+    <t>societe generale private banking - sgpb</t>
+  </si>
+  <si>
+    <t>Mathieu oversees the investment strategy for alternative assets—such as private equity, private debt, and infrastructure—within Societe Generale’s European wealth management division. He sources, selects, and manages non-public investment vehicles for ultra-high-net-worth clients, helping them diversify portfolios beyond traditional stock and bond markets to generate long-term, illiquid returns.</t>
+  </si>
+  <si>
+    <t>Ruben BOTBOL</t>
+  </si>
+  <si>
+    <t>SOCIETE GENERALE SECURITIES SERVICES</t>
+  </si>
+  <si>
+    <t>https://fr.linkedin.com/in/rubenbotbol</t>
+  </si>
+  <si>
+    <t>Ruben Botbol - Alter Domus - LinkedIn</t>
+  </si>
+  <si>
+    <t>Expérience : Alter Domus · Formation : PSB Paris School of Business · Lieu : Paris · 500 relations ou plus sur LinkedIn. Consultez le profil de Ruben Botbol ...</t>
+  </si>
+  <si>
+    <t>sales &amp; relationship manager</t>
+  </si>
+  <si>
+    <t>societe generale securities services - sgss</t>
+  </si>
+  <si>
+    <t>Ruben manages institutional client portfolios for Société Générale Securities Services. He acts as the primary bridge between the bank and asset managers, pension funds, or insurance companies, overseeing the delivery of post-trade services like fund administration, global custody, and clearing to ensure operational efficiency and long-term business retention.</t>
   </si>
 </sst>
 </file>
@@ -413,21 +464,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="146.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="255.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="57.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="63.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="134.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="33.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="255.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -458,16 +509,19 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -479,16 +533,89 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2">
         <v>2</v>
       </c>
-      <c r="J2" t="s">
-        <v>17</v>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
